--- a/data/talks.xlsx
+++ b/data/talks.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{206BA334-C831-4E33-9EEC-AFAAFDD928DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8045D231-EB3F-456D-B20F-9CE1A8F327C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="15480" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tabelle1!$A$1:$M$136</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tabelle1!$A$1:$M$137</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="111">
   <si>
     <t>Title</t>
   </si>
@@ -360,6 +360,15 @@
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=6Rmd1nQnLb4</t>
+  </si>
+  <si>
+    <t>EORTC p-value workshop</t>
+  </si>
+  <si>
+    <t>Decision making versus inference. p-values are not the issue.</t>
+  </si>
+  <si>
+    <t>files/talks/20250930_Rufibach_EORTC_pvalues.pdf</t>
   </si>
 </sst>
 </file>
@@ -811,7 +820,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N29"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
@@ -879,481 +888,480 @@
       <c r="A2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="3">
+        <v>45960</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="2" t="str">
         <f>"06.05.2025"</f>
         <v>06.05.2025</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="2" t="str">
+    <row r="4" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="2" t="str">
         <f>"20.03.2025"</f>
         <v>20.03.2025</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="2" t="str">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="2" t="str">
         <f>"19.03.2025"</f>
         <v>19.03.2025</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="2" t="str">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="2" t="str">
         <f>"23.01.2025"</f>
         <v>23.01.2025</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="2" t="str">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="2" t="str">
         <f>"19.11.2024"</f>
         <v>19.11.2024</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="3" t="str">
+    <row r="8" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="3" t="str">
         <f>"07.11.2024"</f>
         <v>07.11.2024</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="K7" s="5"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="2" t="str">
+      <c r="K8" s="5"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="2" t="str">
         <f>"11.09.2024"</f>
         <v>11.09.2024</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="2" t="str">
+    <row r="10" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="2" t="str">
         <f>"23.05.2024"</f>
         <v>23.05.2024</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F10" s="4" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="168.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="2" t="str">
+    <row r="11" spans="1:14" ht="168.75" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="2" t="str">
         <f>"15.02.2024"</f>
         <v>15.02.2024</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="K11" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="3" t="str">
+    <row r="12" spans="1:14" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="3" t="str">
         <f>"23.10.2023"</f>
         <v>23.10.2023</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C12" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="2" t="str">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="2" t="str">
         <f>"12.10.2023"</f>
         <v>12.10.2023</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="2" t="str">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="2" t="str">
         <f>"18.09.2023"</f>
         <v>18.09.2023</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C14" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="3" t="str">
+    <row r="15" spans="1:14" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="3" t="str">
         <f>"30.08.2023"</f>
         <v>30.08.2023</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M14" s="1" t="s">
+      <c r="M15" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="N14" s="2" t="s">
+      <c r="N15" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="3" t="str">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="3" t="str">
         <f>"09.08.2023"</f>
         <v>09.08.2023</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="56.25" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="3" t="str">
+    <row r="17" spans="1:14" ht="56.25" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="str">
         <f>"12.04.2023"</f>
         <v>12.04.2023</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C17" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D17" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E17" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="M16" s="1" t="s">
+      <c r="M17" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="N16" s="2" t="s">
+      <c r="N17" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="str">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2" t="str">
         <f>"08.08.2022"</f>
         <v>08.08.2022</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C18" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D18" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="2" t="str">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="2" t="str">
         <f>"22.02.2022"</f>
         <v>22.02.2022</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C19" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19" s="2" t="str">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="2" t="str">
         <f>"16.12.2021"</f>
         <v>16.12.2021</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C20" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B20" s="2" t="str">
+    <row r="21" spans="1:14" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="2" t="str">
         <f>"19.05.2021"</f>
         <v>19.05.2021</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C21" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E21" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="M20" s="1" t="s">
+      <c r="M21" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B21" s="3" t="str">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="3" t="str">
         <f>"11.02.2021"</f>
         <v>11.02.2021</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C22" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B22" s="2" t="str">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" s="2" t="str">
         <f>"20.12.2020"</f>
         <v>20.12.2020</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C23" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D23" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A23" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B23" s="3" t="str">
+    <row r="24" spans="1:14" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" s="3" t="str">
         <f>"23.05.2019"</f>
         <v>23.05.2019</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C24" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D24" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A24" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B24" s="3" t="str">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25" s="3" t="str">
         <f>"10.09.2018"</f>
         <v>10.09.2018</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C25" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E25" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B25" s="3" t="str">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B26" s="3" t="str">
         <f>"28.04.2016"</f>
         <v>28.04.2016</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C26" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D26" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E26" s="2" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A26" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B26" s="3" t="str">
-        <f>"19.06.2024"</f>
-        <v>19.06.2024</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="22.5" x14ac:dyDescent="0.2">
@@ -1361,23 +1369,17 @@
         <v>18</v>
       </c>
       <c r="B27" s="3" t="str">
-        <f>"28.08.2023"</f>
-        <v>28.08.2023</v>
+        <f>"19.06.2024"</f>
+        <v>19.06.2024</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M27" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N27" s="2" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="22.5" x14ac:dyDescent="0.2">
@@ -1385,17 +1387,23 @@
         <v>18</v>
       </c>
       <c r="B28" s="3" t="str">
-        <f>"22.08.2022                         "</f>
-        <v xml:space="preserve">22.08.2022                         </v>
+        <f>"28.08.2023"</f>
+        <v>28.08.2023</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="22.5" x14ac:dyDescent="0.2">
@@ -1403,29 +1411,47 @@
         <v>18</v>
       </c>
       <c r="B29" s="3" t="str">
+        <f>"22.08.2022                         "</f>
+        <v xml:space="preserve">22.08.2022                         </v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B30" s="3" t="str">
         <f>"16.06.2015"</f>
         <v>16.06.2015</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C30" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D30" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E30" s="2" t="s">
         <v>62</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A9:N27">
-    <sortCondition descending="1" ref="A9:A27"/>
-    <sortCondition descending="1" ref="B9:B27"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A10:N28">
+    <sortCondition descending="1" ref="A10:A28"/>
+    <sortCondition descending="1" ref="B10:B28"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="E16" r:id="rId1" location="quantification-of-risk-ask-the-right-questions-or-time-to-apply-the-estimand-framework-to-safety" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="F9" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="F3" r:id="rId3" xr:uid="{A9F0675B-0F44-448E-A757-25BD626F7097}"/>
+    <hyperlink ref="E17" r:id="rId1" location="quantification-of-risk-ask-the-right-questions-or-time-to-apply-the-estimand-framework-to-safety" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="F10" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="F4" r:id="rId3" xr:uid="{A9F0675B-0F44-448E-A757-25BD626F7097}"/>
   </hyperlinks>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0527777777777778" bottom="1.0527777777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId4"/>

--- a/data/talks.xlsx
+++ b/data/talks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8045D231-EB3F-456D-B20F-9CE1A8F327C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F84EC6C-9D28-48C2-BEA4-12597EED4497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="15480" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -888,8 +888,9 @@
       <c r="A2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="3">
-        <v>45960</v>
+      <c r="B2" s="3" t="str">
+        <f>"30.09.2025"</f>
+        <v>30.09.2025</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>108</v>

--- a/data/talks.xlsx
+++ b/data/talks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F84EC6C-9D28-48C2-BEA4-12597EED4497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB8614B3-9C4B-46A5-88FA-86190C4C58A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="15480" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="720" windowWidth="28800" windowHeight="15480" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="112">
   <si>
     <t>Title</t>
   </si>
@@ -369,6 +369,9 @@
   </si>
   <si>
     <t>files/talks/20250930_Rufibach_EORTC_pvalues.pdf</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/posts/kasparrufibach_biostatistics-collaboration-activity-7377702182470443008-EFvl?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAAQJ2qsB_r_XsYhAPWyf_WQeC5V6NOcbIXo</t>
   </si>
 </sst>
 </file>
@@ -884,7 +887,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>16</v>
       </c>
@@ -901,6 +904,9 @@
       <c r="E2" s="2" t="s">
         <v>110</v>
       </c>
+      <c r="K2" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="3" spans="1:14" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -1059,7 +1065,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="168.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" ht="157.5" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -1076,7 +1082,7 @@
       <c r="E11" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="L11" s="2" t="s">
         <v>65</v>
       </c>
     </row>

--- a/data/talks.xlsx
+++ b/data/talks.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB8614B3-9C4B-46A5-88FA-86190C4C58A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61402FB5-69A5-4EA2-8ADF-E70272611C89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="720" windowWidth="28800" windowHeight="15480" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tabelle1!$A$1:$M$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tabelle1!$A$1:$M$138</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="115">
   <si>
     <t>Title</t>
   </si>
@@ -372,6 +372,15 @@
   </si>
   <si>
     <t>https://www.linkedin.com/posts/kasparrufibach_biostatistics-collaboration-activity-7377702182470443008-EFvl?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAAQJ2qsB_r_XsYhAPWyf_WQeC5V6NOcbIXo</t>
+  </si>
+  <si>
+    <t>WHO adaptive platform trials working group</t>
+  </si>
+  <si>
+    <t>Platform trials: some considerations from a statistician</t>
+  </si>
+  <si>
+    <t>files/talks/20260311_WHO_platform_Rufibach.pdf</t>
   </si>
 </sst>
 </file>
@@ -823,7 +832,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
@@ -887,506 +896,506 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="3" t="str">
+      <c r="B2" s="2" t="str">
+        <f>"11.03.2026"</f>
+        <v>11.03.2026</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="3" t="str">
         <f>"30.09.2025"</f>
         <v>30.09.2025</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K3" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="2" t="str">
+    <row r="4" spans="1:14" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="2" t="str">
         <f>"06.05.2025"</f>
         <v>06.05.2025</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="2" t="str">
+    <row r="5" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="2" t="str">
         <f>"20.03.2025"</f>
         <v>20.03.2025</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="2" t="str">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="2" t="str">
         <f>"19.03.2025"</f>
         <v>19.03.2025</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="2" t="str">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="2" t="str">
         <f>"23.01.2025"</f>
         <v>23.01.2025</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="2" t="str">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="2" t="str">
         <f>"19.11.2024"</f>
         <v>19.11.2024</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="3" t="str">
+    <row r="9" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="3" t="str">
         <f>"07.11.2024"</f>
         <v>07.11.2024</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="K8" s="5"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="2" t="str">
+      <c r="K9" s="5"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="2" t="str">
         <f>"11.09.2024"</f>
         <v>11.09.2024</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="2" t="str">
+    <row r="11" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="2" t="str">
         <f>"23.05.2024"</f>
         <v>23.05.2024</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F11" s="4" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="157.5" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="2" t="str">
+    <row r="12" spans="1:14" ht="157.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="2" t="str">
         <f>"15.02.2024"</f>
         <v>15.02.2024</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C12" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="L11" s="2" t="s">
+      <c r="L12" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="3" t="str">
+    <row r="13" spans="1:14" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="3" t="str">
         <f>"23.10.2023"</f>
         <v>23.10.2023</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="2" t="str">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="2" t="str">
         <f>"12.10.2023"</f>
         <v>12.10.2023</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C14" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="2" t="str">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="2" t="str">
         <f>"18.09.2023"</f>
         <v>18.09.2023</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C15" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="3" t="str">
+    <row r="16" spans="1:14" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="3" t="str">
         <f>"30.08.2023"</f>
         <v>30.08.2023</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M15" s="1" t="s">
+      <c r="M16" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="N15" s="2" t="s">
+      <c r="N16" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="3" t="str">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="str">
         <f>"09.08.2023"</f>
         <v>09.08.2023</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C17" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="56.25" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="3" t="str">
+    <row r="18" spans="1:14" ht="56.25" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="3" t="str">
         <f>"12.04.2023"</f>
         <v>12.04.2023</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C18" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D18" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E18" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="M17" s="1" t="s">
+      <c r="M18" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="N17" s="2" t="s">
+      <c r="N18" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="2" t="str">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="2" t="str">
         <f>"08.08.2022"</f>
         <v>08.08.2022</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C19" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19" s="2" t="str">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="2" t="str">
         <f>"22.02.2022"</f>
         <v>22.02.2022</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C20" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B20" s="2" t="str">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="2" t="str">
         <f>"16.12.2021"</f>
         <v>16.12.2021</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C21" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E21" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B21" s="2" t="str">
+    <row r="22" spans="1:14" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="2" t="str">
         <f>"19.05.2021"</f>
         <v>19.05.2021</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C22" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="M21" s="1" t="s">
+      <c r="M22" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B22" s="3" t="str">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" s="3" t="str">
         <f>"11.02.2021"</f>
         <v>11.02.2021</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C23" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D23" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A23" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B23" s="2" t="str">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" s="2" t="str">
         <f>"20.12.2020"</f>
         <v>20.12.2020</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C24" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D24" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A24" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B24" s="3" t="str">
+    <row r="25" spans="1:14" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25" s="3" t="str">
         <f>"23.05.2019"</f>
         <v>23.05.2019</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C25" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E25" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B25" s="3" t="str">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B26" s="3" t="str">
         <f>"10.09.2018"</f>
         <v>10.09.2018</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C26" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E26" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A26" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B26" s="3" t="str">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" s="3" t="str">
         <f>"28.04.2016"</f>
         <v>28.04.2016</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C27" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D27" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E27" s="2" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A27" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B27" s="3" t="str">
-        <f>"19.06.2024"</f>
-        <v>19.06.2024</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="22.5" x14ac:dyDescent="0.2">
@@ -1394,23 +1403,17 @@
         <v>18</v>
       </c>
       <c r="B28" s="3" t="str">
-        <f>"28.08.2023"</f>
-        <v>28.08.2023</v>
+        <f>"19.06.2024"</f>
+        <v>19.06.2024</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M28" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N28" s="2" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="22.5" x14ac:dyDescent="0.2">
@@ -1418,17 +1421,23 @@
         <v>18</v>
       </c>
       <c r="B29" s="3" t="str">
-        <f>"22.08.2022                         "</f>
-        <v xml:space="preserve">22.08.2022                         </v>
+        <f>"28.08.2023"</f>
+        <v>28.08.2023</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="22.5" x14ac:dyDescent="0.2">
@@ -1436,29 +1445,47 @@
         <v>18</v>
       </c>
       <c r="B30" s="3" t="str">
+        <f>"22.08.2022                         "</f>
+        <v xml:space="preserve">22.08.2022                         </v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B31" s="3" t="str">
         <f>"16.06.2015"</f>
         <v>16.06.2015</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C31" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D31" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E31" s="2" t="s">
         <v>62</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A10:N28">
-    <sortCondition descending="1" ref="A10:A28"/>
-    <sortCondition descending="1" ref="B10:B28"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:N29">
+    <sortCondition descending="1" ref="A11:A29"/>
+    <sortCondition descending="1" ref="B11:B29"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="E17" r:id="rId1" location="quantification-of-risk-ask-the-right-questions-or-time-to-apply-the-estimand-framework-to-safety" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="F10" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="F4" r:id="rId3" xr:uid="{A9F0675B-0F44-448E-A757-25BD626F7097}"/>
+    <hyperlink ref="E18" r:id="rId1" location="quantification-of-risk-ask-the-right-questions-or-time-to-apply-the-estimand-framework-to-safety" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="F11" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="F5" r:id="rId3" xr:uid="{A9F0675B-0F44-448E-A757-25BD626F7097}"/>
   </hyperlinks>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0527777777777778" bottom="1.0527777777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId4"/>
